--- a/analysis_data/getting_atc_parameters.xlsx
+++ b/analysis_data/getting_atc_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kadekola\github_codes\cross_border-CM\analysis_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365BF863-3ED3-491D-A785-E2F5E36FD94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169EBC24-012D-4C7A-953D-D78D8E006A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="1700" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="locational_const" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="90">
   <si>
     <t>locational signal</t>
   </si>
@@ -109,12 +109,18 @@
     <t>Price cap</t>
   </si>
   <si>
+    <t>─────┼────────────────────────────────</t>
+  </si>
+  <si>
     <t>No CBP</t>
   </si>
   <si>
     <t>Demand during scarcity</t>
   </si>
   <si>
+    <t>5×3</t>
+  </si>
+  <si>
     <t>DataFrame</t>
   </si>
   <si>
@@ -166,125 +172,149 @@
     <t>ATC:</t>
   </si>
   <si>
-    <t>[(2011.9740924491018,</t>
-  </si>
-  <si>
-    <t>-1236.7105009942327),</t>
-  </si>
-  <si>
-    <t>(1221.2694990057487,</t>
-  </si>
-  <si>
-    <t>-1996.648685892471),</t>
-  </si>
-  <si>
-    <t>(363.91868589247133,</t>
-  </si>
-  <si>
-    <t>-1139.5909075508825)]</t>
-  </si>
-  <si>
     <t>Dict((:A,</t>
   </si>
   <si>
     <t>=&gt;</t>
   </si>
   <si>
-    <t>(2011.9740924491018,</t>
-  </si>
-  <si>
-    <t>-1139.5909075508825))</t>
-  </si>
-  <si>
     <t>Simultaneous scarcity</t>
   </si>
   <si>
     <t>Scarcity at A</t>
   </si>
   <si>
-    <t>[(989.8932684992363,</t>
-  </si>
-  <si>
-    <t>-504.528291665285),</t>
-  </si>
-  <si>
-    <t>(1150.05172806395,</t>
-  </si>
-  <si>
-    <t>-1635.4048089345201),</t>
-  </si>
-  <si>
-    <t>(650.0251910654783,</t>
-  </si>
-  <si>
-    <t>-164.67825863461846)]</t>
-  </si>
-  <si>
-    <t>(989.8932684992363,</t>
-  </si>
-  <si>
-    <t>-164.67825863461846))</t>
-  </si>
-  <si>
     <t>Scarcity at B</t>
   </si>
   <si>
-    <t>[(2136.663670745699,</t>
-  </si>
-  <si>
-    <t>-1255.60100480321),</t>
-  </si>
-  <si>
-    <t>(398.97899519677725,</t>
-  </si>
-  <si>
-    <t>-1456.7183322728788),</t>
-  </si>
-  <si>
-    <t>(476.6883462946189,</t>
-  </si>
-  <si>
-    <t>-1798.8826725303256)]</t>
-  </si>
-  <si>
-    <t>(2136.663670745699,</t>
-  </si>
-  <si>
-    <t>-1798.8826725303256))</t>
-  </si>
-  <si>
     <t>Scarcity at C</t>
   </si>
   <si>
-    <t>[(2528.9409161241756,</t>
-  </si>
-  <si>
-    <t>-1753.7153152159585),</t>
-  </si>
-  <si>
-    <t>(1507.6646847840316,</t>
-  </si>
-  <si>
-    <t>-2437.9871484908886),</t>
-  </si>
-  <si>
-    <t>(152.55714849089054,</t>
-  </si>
-  <si>
-    <t>-1315.7281667250718)]</t>
-  </si>
-  <si>
-    <t>(2528.9409161241756,</t>
-  </si>
-  <si>
-    <t>-1315.7281667250718))</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Derived from central planner</t>
+  </si>
+  <si>
+    <t>Capacity demand for FBMC</t>
+  </si>
+  <si>
+    <t>Capacity demand for explicit</t>
+  </si>
+  <si>
+    <t>Capacity demand for implicit</t>
+  </si>
+  <si>
+    <t>perfect foresightof scarcity and imports</t>
+  </si>
+  <si>
+    <t>[(2246.2890576658883,</t>
+  </si>
+  <si>
+    <t>-1924.0114138595968),</t>
+  </si>
+  <si>
+    <t>(336.5885861403943,</t>
+  </si>
+  <si>
+    <t>-658.7893222160648),</t>
+  </si>
+  <si>
+    <t>(783.5895291913974,</t>
+  </si>
+  <si>
+    <t>-1105.8610458217672)]</t>
+  </si>
+  <si>
+    <t>(2246.2890576658883,</t>
+  </si>
+  <si>
+    <t>-1105.8610458217672))</t>
+  </si>
+  <si>
+    <t>[(1110.5750000000266,</t>
+  </si>
+  <si>
+    <t>-1110.5750000000266),</t>
+  </si>
+  <si>
+    <t>(257.32500000002506,</t>
+  </si>
+  <si>
+    <t>-257.32500000002506),</t>
+  </si>
+  <si>
+    <t>(343.17499999998194,</t>
+  </si>
+  <si>
+    <t>-343.17499999998205)]</t>
+  </si>
+  <si>
+    <t>(1110.5750000000266,</t>
+  </si>
+  <si>
+    <t>-343.17499999998205))</t>
+  </si>
+  <si>
+    <t>[(3000.0,</t>
+  </si>
+  <si>
+    <t>-2402.1501554283323),</t>
+  </si>
+  <si>
+    <t>(751.0498445716504,</t>
+  </si>
+  <si>
+    <t>-1548.0701515511914),</t>
+  </si>
+  <si>
+    <t>(947.5701515511914,</t>
+  </si>
+  <si>
+    <t>-2143.3400019385663)]</t>
+  </si>
+  <si>
+    <t>(3000.0,</t>
+  </si>
+  <si>
+    <t>-2143.3400019385663))</t>
+  </si>
+  <si>
+    <t>[(2712.2951333043493,</t>
+  </si>
+  <si>
+    <t>-1770.4528585147475),</t>
+  </si>
+  <si>
+    <t>(402.55285851475327,</t>
+  </si>
+  <si>
+    <t>-539.2430206400088),</t>
+  </si>
+  <si>
+    <t>(1389.2432117668968,</t>
+  </si>
+  <si>
+    <t>-2331.904918937371)]</t>
+  </si>
+  <si>
+    <t>(2712.2951333043493,</t>
+  </si>
+  <si>
+    <t>-2331.904918937371))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +343,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -322,7 +359,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -330,11 +367,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -358,6 +457,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,130 +774,138 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
       <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
         <v>31</v>
       </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6">
-        <v>40053.5</v>
-      </c>
-      <c r="F6">
-        <v>50135.1</v>
-      </c>
-      <c r="G6">
-        <v>61008.9</v>
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>40053.5</v>
+        <v>45897.4</v>
       </c>
       <c r="F7">
-        <v>50135.1</v>
+        <v>51034.8</v>
       </c>
       <c r="G7">
-        <v>61008.9</v>
+        <v>56157.599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>1993.53</v>
+        <v>45897.4</v>
       </c>
       <c r="F8">
-        <v>341.29500000000002</v>
+        <v>51034.8</v>
       </c>
       <c r="G8">
-        <v>1831.2</v>
+        <v>56157.599999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="C9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>40053.5</v>
+        <v>2017.63</v>
       </c>
       <c r="F9">
-        <v>50135.1</v>
+        <v>320.00099999999998</v>
       </c>
       <c r="G9">
-        <v>61008.9</v>
+        <v>1727.89</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10">
+        <v>45897.4</v>
+      </c>
+      <c r="F10">
+        <v>51034.8</v>
+      </c>
+      <c r="G10">
+        <v>56157.599999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C11">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <v>8939.5</v>
-      </c>
-      <c r="F10">
-        <v>6467.8</v>
-      </c>
-      <c r="G10">
-        <v>4998.57</v>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11">
+        <v>9711.32</v>
+      </c>
+      <c r="F11">
+        <v>6853.67</v>
+      </c>
+      <c r="G11">
+        <v>4599.08</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -788,38 +915,38 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -827,16 +954,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16">
-        <v>47131.9</v>
+        <v>55667.5</v>
       </c>
       <c r="F16">
-        <v>62913.9</v>
+        <v>69013.3</v>
       </c>
       <c r="G16">
-        <v>73354.100000000006</v>
+        <v>75320.100000000006</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -844,16 +971,16 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>47131.9</v>
+        <v>55667.5</v>
       </c>
       <c r="F17">
-        <v>62913.9</v>
+        <v>69013.3</v>
       </c>
       <c r="G17">
-        <v>73354.100000000006</v>
+        <v>75320.100000000006</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -861,16 +988,16 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>1266.8800000000001</v>
+        <v>1489.58</v>
       </c>
       <c r="F18">
-        <v>472.83100000000002</v>
+        <v>524.22799999999995</v>
       </c>
       <c r="G18">
-        <v>1003.57</v>
+        <v>948.27200000000005</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -878,16 +1005,16 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19">
-        <v>47131.9</v>
+        <v>55667.5</v>
       </c>
       <c r="F19">
-        <v>62913.9</v>
+        <v>69013.3</v>
       </c>
       <c r="G19">
-        <v>73354.100000000006</v>
+        <v>75320.100000000006</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -895,16 +1022,16 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20">
-        <v>11581.1</v>
+        <v>13968.6</v>
       </c>
       <c r="F20">
-        <v>8574.27</v>
+        <v>9368</v>
       </c>
       <c r="G20">
-        <v>3641.93</v>
+        <v>3536.64</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -914,33 +1041,33 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -953,13 +1080,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F26">
-        <v>67591.3</v>
+        <v>73866.3</v>
       </c>
       <c r="G26">
         <v>80000</v>
@@ -970,13 +1097,13 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E27">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F27">
-        <v>67591.3</v>
+        <v>73866.3</v>
       </c>
       <c r="G27">
         <v>80000</v>
@@ -987,16 +1114,16 @@
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F28">
-        <v>66181.3</v>
+        <v>73866.3</v>
       </c>
       <c r="G28">
-        <v>78683</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1004,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F29">
-        <v>67591.3</v>
+        <v>73866.3</v>
       </c>
       <c r="G29">
         <v>80000</v>
@@ -1021,16 +1148,16 @@
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F30">
-        <v>66436.100000000006</v>
+        <v>73866.3</v>
       </c>
       <c r="G30">
-        <v>78857.600000000006</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -1040,33 +1167,33 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1079,16 +1206,16 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E37">
-        <v>59476.4</v>
+        <v>70000</v>
       </c>
       <c r="F37">
-        <v>67393.2</v>
+        <v>72538.899999999994</v>
       </c>
       <c r="G37">
-        <v>77466.5</v>
+        <v>77631.5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -1096,16 +1223,16 @@
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E38">
-        <v>59476.4</v>
+        <v>70000</v>
       </c>
       <c r="F38">
-        <v>67393.2</v>
+        <v>72538.899999999994</v>
       </c>
       <c r="G38">
-        <v>77466.5</v>
+        <v>77631.5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -1113,16 +1240,16 @@
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E39">
-        <v>56393.2</v>
+        <v>70000</v>
       </c>
       <c r="F39">
-        <v>37258.1</v>
+        <v>71017.399999999994</v>
       </c>
       <c r="G39">
-        <v>19618.8</v>
+        <v>68030.7</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -1130,16 +1257,16 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E40">
-        <v>59476.4</v>
+        <v>70000</v>
       </c>
       <c r="F40">
-        <v>67393.2</v>
+        <v>72538.899999999994</v>
       </c>
       <c r="G40">
-        <v>77466.5</v>
+        <v>77631.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -1147,16 +1274,16 @@
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E41">
-        <v>57168.1</v>
+        <v>70000</v>
       </c>
       <c r="F41">
-        <v>41034.5</v>
+        <v>71292.399999999994</v>
       </c>
       <c r="G41">
-        <v>21689.1</v>
+        <v>68221.3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -1166,42 +1293,42 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1210,16 +1337,16 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E48">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F48">
-        <v>67499.100000000006</v>
+        <v>73691</v>
       </c>
       <c r="G48">
-        <v>77558.5</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -1227,16 +1354,16 @@
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E49">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F49">
-        <v>67499.100000000006</v>
+        <v>73691</v>
       </c>
       <c r="G49">
-        <v>77558.5</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -1244,16 +1371,16 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E50">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F50">
-        <v>60051.4</v>
+        <v>72059.5</v>
       </c>
       <c r="G50">
-        <v>60796.6</v>
+        <v>79047.5</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -1261,16 +1388,16 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E51">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F51">
-        <v>67499.100000000006</v>
+        <v>73691</v>
       </c>
       <c r="G51">
-        <v>77558.5</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -1278,16 +1405,16 @@
         <v>5</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E52">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="F52">
-        <v>61055.9</v>
+        <v>72334.600000000006</v>
       </c>
       <c r="G52">
-        <v>61363.1</v>
+        <v>79173.8</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -1295,40 +1422,40 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C56" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C57" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -1336,16 +1463,16 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E60">
-        <v>80000</v>
+        <v>70000</v>
       </c>
       <c r="F60">
-        <v>69871.7</v>
+        <v>72503.399999999994</v>
       </c>
       <c r="G60">
-        <v>60000</v>
+        <v>77579.899999999994</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -1353,16 +1480,16 @@
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E61">
-        <v>80000</v>
+        <v>70000</v>
       </c>
       <c r="F61">
-        <v>69871.7</v>
+        <v>72503.399999999994</v>
       </c>
       <c r="G61">
-        <v>60000</v>
+        <v>77579.899999999994</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -1370,16 +1497,16 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E62">
-        <v>79965.100000000006</v>
+        <v>70000</v>
       </c>
       <c r="F62">
-        <v>66668</v>
+        <v>70009.3</v>
       </c>
       <c r="G62">
-        <v>60000</v>
+        <v>70699.8</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -1387,16 +1514,16 @@
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E63">
-        <v>80000</v>
+        <v>70000</v>
       </c>
       <c r="F63">
-        <v>69871.7</v>
+        <v>72503.399999999994</v>
       </c>
       <c r="G63">
-        <v>60000</v>
+        <v>77579.899999999994</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -1404,16 +1531,16 @@
         <v>5</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E64">
-        <v>79971.8</v>
+        <v>70000</v>
       </c>
       <c r="F64">
-        <v>66959.399999999994</v>
+        <v>70405.7</v>
       </c>
       <c r="G64">
-        <v>60000</v>
+        <v>70912.600000000006</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA28A093-846C-4F3B-8C78-08E6801904D8}">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="5.1796875" customWidth="1"/>
@@ -1436,10 +1563,12 @@
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="8" max="8" width="14.7265625" customWidth="1"/>
     <col min="12" max="12" width="10.6328125" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.54296875" customWidth="1"/>
+    <col min="18" max="18" width="1.6328125" customWidth="1"/>
+    <col min="19" max="19" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1449,7 +1578,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -1457,7 +1586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1468,56 +1597,64 @@
         <v>16</v>
       </c>
       <c r="H3">
-        <v>21189.5348933694</v>
+        <v>20553.050692503999</v>
       </c>
       <c r="I3">
-        <v>5731.5403867180603</v>
+        <v>6419.1957387682496</v>
       </c>
       <c r="J3">
-        <v>7876.4533245359198</v>
+        <v>8301.4954943629691</v>
       </c>
       <c r="K3">
-        <v>10232.0526608256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+        <v>9641.3182327304094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4">
-        <v>32424.3489741062</v>
+        <v>31838.857004241901</v>
       </c>
       <c r="F4">
         <f>SUM(H3:H7)</f>
-        <v>32839.447757407404</v>
+        <v>30161.610316376529</v>
+      </c>
+      <c r="G4">
+        <f>SUM(D4:D5)</f>
+        <v>45192.728483988903</v>
       </c>
       <c r="H4">
-        <v>4886.0618148282001</v>
+        <v>4570.7761766125705</v>
       </c>
       <c r="I4">
-        <v>2946.3215454373699</v>
+        <v>3063.4327105391098</v>
       </c>
       <c r="J4">
-        <v>1100.7902057511401</v>
+        <v>1216.6965776993</v>
       </c>
       <c r="K4">
-        <v>2034.8589838826199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>2221.66346456981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5">
-        <v>13843.7723412952</v>
+        <v>13353.871479747</v>
       </c>
       <c r="F5">
         <f>SUM(I3:I7)</f>
-        <v>12254.83200458403</v>
+        <v>12753.466061143241</v>
+      </c>
+      <c r="G5">
+        <f>SUM(F4:F5)</f>
+        <v>42915.07637751977</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1532,44 +1669,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="7"/>
       <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6">
-        <v>10538.3592852661</v>
+        <v>10412.5465916298</v>
       </c>
       <c r="F6">
         <f>SUM(J3:J7)</f>
-        <v>10215.244239412259</v>
+        <v>10773.516150583449</v>
       </c>
       <c r="H6">
-        <v>6763.8510492098003</v>
+        <v>5037.7834472599598</v>
       </c>
       <c r="I6">
-        <v>3576.9700724285999</v>
+        <v>3270.8376118358801</v>
       </c>
       <c r="J6">
-        <v>1238.0007091252</v>
+        <v>1255.3240785211799</v>
       </c>
       <c r="K6">
-        <v>1914.8076302832601</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <v>1957.20466786251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7">
-        <v>11790.2868971441</v>
+        <v>11594.3720628314</v>
       </c>
       <c r="F7">
         <f>SUM(K3:K7)</f>
-        <v>14181.719274991479</v>
+        <v>13820.18636516273</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1584,21 +1721,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="5">
         <f>SUM(D4:D7)</f>
-        <v>68596.767497811597</v>
+        <v>67199.647138450106</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5">
         <f>SUM(F4:F7)</f>
-        <v>69491.24327639518</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <v>67508.778893265946</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
@@ -1608,70 +1745,78 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10">
-        <v>24341.2826266599</v>
+        <v>24582.814326698201</v>
       </c>
       <c r="F10">
         <f>SUM(H10:H14)</f>
-        <v>24121.504448781809</v>
+        <v>24328.312939775838</v>
+      </c>
+      <c r="G10">
+        <f>SUM(D10:D11)</f>
+        <v>33522.686203097903</v>
       </c>
       <c r="H10">
-        <v>19560.589943229199</v>
+        <v>19878.5927050555</v>
       </c>
       <c r="I10">
-        <v>5703.7443581151801</v>
+        <v>5479.4785871971899</v>
       </c>
       <c r="J10">
-        <v>8903.0366884744599</v>
+        <v>8997.3552790589092</v>
       </c>
       <c r="K10">
-        <v>10177.643294380199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <v>9817.1056173450506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11">
-        <v>9315.4865216555609</v>
+        <v>8939.8718763997003</v>
       </c>
       <c r="F11">
         <f>SUM(I10:I14)</f>
-        <v>8798.8037135767481</v>
+        <v>8472.5814712016418</v>
+      </c>
+      <c r="G11">
+        <f>SUM(F10:F11)</f>
+        <v>32800.894410977482</v>
       </c>
       <c r="H11">
-        <v>3817.3983150394602</v>
+        <v>3742.66040444483</v>
       </c>
       <c r="I11">
-        <v>2455.4452745763701</v>
+        <v>2385.1603031363402</v>
       </c>
       <c r="J11">
-        <v>2280.7515833161401</v>
+        <v>2336.9444082216801</v>
       </c>
       <c r="K11">
-        <v>2348.6961651909801</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>2665.0273956394799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12">
-        <v>13876.531717096899</v>
+        <v>14000.609851065101</v>
       </c>
       <c r="F12">
         <f>SUM(J10:J14)</f>
-        <v>12913.56286070944</v>
+        <v>13018.645624896419</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1686,42 +1831,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13">
-        <v>12994.9074500958</v>
+        <v>12991.0577834386</v>
       </c>
       <c r="F13">
         <f>SUM(K10:K14)</f>
-        <v>14700.089444367379</v>
+        <v>14699.94246519664</v>
       </c>
       <c r="H13">
-        <v>743.51619051315095</v>
+        <v>707.05983027550894</v>
       </c>
       <c r="I13">
-        <v>639.61408088519795</v>
+        <v>607.94258086811203</v>
       </c>
       <c r="J13">
-        <v>1729.77458891884</v>
+        <v>1684.3459376158301</v>
       </c>
       <c r="K13">
-        <v>2173.7499847961999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>2217.80945221211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="D14" s="5">
         <f>SUM(D10:D13)</f>
-        <v>60528.208315508164</v>
+        <v>60514.3538376016</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5">
         <f>SUM(F10:F13)</f>
-        <v>60533.960467435376</v>
+        <v>60519.482501070539</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1736,12 +1881,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>17</v>
@@ -1756,529 +1901,682 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16">
-        <v>45101.478732900403</v>
+        <v>47375.413458884999</v>
       </c>
       <c r="F16">
-        <v>43980.3</v>
+        <v>46499.4</v>
+      </c>
+      <c r="G16">
+        <f>SUM(D16:D17)</f>
+        <v>71032.150000432099</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>42512.7</v>
+        <v>47236.4</v>
       </c>
       <c r="J16">
-        <v>18219.7</v>
+        <v>20244.2</v>
       </c>
       <c r="K16">
-        <v>12401.9</v>
+        <v>13779.9</v>
       </c>
       <c r="L16">
-        <v>15264.8</v>
+        <v>16960.900000000001</v>
       </c>
       <c r="M16">
         <f>SUM(I16:L16)</f>
-        <v>88399.099999999991</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+        <v>98221.4</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="15"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
       <c r="B17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17">
-        <v>18827.456268573998</v>
+        <v>23656.736541547099</v>
       </c>
       <c r="F17">
-        <v>19948.7</v>
+        <v>24532.7</v>
+      </c>
+      <c r="G17">
+        <f>SUM(F16:F17)</f>
+        <v>71032.100000000006</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I17">
-        <v>44750.3</v>
+        <v>49722.5</v>
       </c>
       <c r="J17">
-        <v>19178.7</v>
+        <v>21309.599999999999</v>
       </c>
       <c r="K17">
-        <v>11749.2</v>
+        <v>13054.6</v>
       </c>
       <c r="L17">
-        <v>14461.4</v>
+        <v>16068.2</v>
       </c>
       <c r="M17">
-        <f t="shared" ref="M17:M25" si="0">SUM(I17:L17)</f>
-        <v>90139.599999999991</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" ref="M17:M19" si="0">SUM(I17:L17)</f>
+        <v>100154.90000000001</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>71032.149999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18">
-        <v>13054.5569106154</v>
+        <v>14505.139964446</v>
       </c>
       <c r="F18">
-        <v>13054.6</v>
+        <v>14505.1</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I18">
-        <v>40275.199999999997</v>
+        <v>44750.3</v>
       </c>
       <c r="J18">
-        <v>17260.8</v>
+        <v>19178.7</v>
       </c>
       <c r="K18">
-        <v>13054.6</v>
+        <v>14505.1</v>
       </c>
       <c r="L18">
-        <v>14461.4</v>
+        <v>16068.2</v>
       </c>
       <c r="M18">
         <f t="shared" si="0"/>
-        <v>85052</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+        <v>94502.3</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>14505.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="7"/>
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19">
-        <v>16068.1899498819</v>
+        <v>17853.548584189601</v>
       </c>
       <c r="F19">
-        <v>16068.2</v>
+        <v>17853.599999999999</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I19">
-        <v>40275.199999999997</v>
+        <v>44750.3</v>
       </c>
       <c r="J19">
-        <v>17260.8</v>
+        <v>19178.7</v>
       </c>
       <c r="K19">
-        <v>11749.2</v>
+        <v>13054.6</v>
       </c>
       <c r="L19">
-        <v>16068.2</v>
+        <v>17853.5</v>
       </c>
       <c r="M19">
         <f t="shared" si="0"/>
-        <v>85353.4</v>
-      </c>
-      <c r="O19">
-        <f>I17+J17+K18+L19</f>
-        <v>93051.8</v>
-      </c>
-      <c r="P19">
-        <v>86919.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+        <v>94837.1</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>17853.55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="D20" s="5">
         <f>SUM(D16:D19)</f>
-        <v>93051.681861971694</v>
+        <v>103390.8385490677</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5">
         <f t="shared" ref="F20" si="1">SUM(F16:F19)</f>
-        <v>93051.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+        <v>103390.80000000002</v>
+      </c>
+      <c r="Q20">
+        <f>SUM(Q17:Q19)</f>
+        <v>103390.84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22">
-        <v>45551.821378897097</v>
-      </c>
-      <c r="F22">
-        <v>44421.2</v>
+        <v>47220.575097456698</v>
+      </c>
+      <c r="F22" s="18">
+        <v>48182.9</v>
       </c>
       <c r="G22">
-        <v>44622.5</v>
+        <f>SUM(D22:D23)</f>
+        <v>72872.874314064902</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>42512.7</v>
+        <v>47236.4</v>
       </c>
       <c r="J22">
-        <v>18219.7</v>
+        <v>20244.2</v>
       </c>
       <c r="K22">
-        <v>12401.9</v>
+        <v>13779.9</v>
       </c>
       <c r="L22">
-        <v>15264.8</v>
+        <v>16960.900000000001</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
-        <v>88399.099999999991</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" ref="M17:M38" si="2">SUM(I22:L22)</f>
+        <v>98221.4</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23">
-        <v>20658.4614301935</v>
-      </c>
-      <c r="F23">
-        <v>20278.5</v>
+        <v>25652.2992166082</v>
+      </c>
+      <c r="F23" s="18">
+        <v>23616.6</v>
       </c>
       <c r="G23">
-        <v>20485.5</v>
+        <f>SUM(F22:F23)</f>
+        <v>71799.5</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I23">
-        <v>44750.3</v>
+        <v>49722.5</v>
       </c>
       <c r="J23">
-        <v>19178.7</v>
+        <v>21309.599999999999</v>
       </c>
       <c r="K23">
-        <v>11749.2</v>
+        <v>13054.6</v>
       </c>
       <c r="L23">
-        <v>14461.4</v>
+        <v>16068.2</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
-        <v>90139.599999999991</v>
-      </c>
-      <c r="O23" s="6">
-        <v>71032.149999999994</v>
-      </c>
-      <c r="P23" s="6">
-        <v>65032.15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>100154.90000000001</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>70327.55</v>
+      </c>
+      <c r="R23" s="17"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24">
-        <v>14034.6296870727</v>
-      </c>
-      <c r="F24">
-        <v>13651.6</v>
-      </c>
-      <c r="G24">
-        <v>13243.5</v>
+        <v>14261.649015321</v>
+      </c>
+      <c r="F24" s="18">
+        <v>13655.1</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I24">
-        <v>40275.199999999997</v>
+        <v>44750.3</v>
       </c>
       <c r="J24">
-        <v>17260.8</v>
+        <v>19178.7</v>
       </c>
       <c r="K24">
-        <v>13054.6</v>
+        <v>14505.1</v>
       </c>
       <c r="L24">
-        <v>14461.4</v>
+        <v>16068.2</v>
       </c>
       <c r="M24">
-        <f t="shared" si="0"/>
-        <v>85052</v>
-      </c>
-      <c r="O24" s="4">
-        <v>14505.14</v>
-      </c>
-      <c r="P24" s="6">
-        <v>13873.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>94502.3</v>
+      </c>
+      <c r="O24" s="4"/>
+      <c r="P24" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>13952.64</v>
+      </c>
+      <c r="R24" s="17"/>
+    </row>
+    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="7"/>
       <c r="B25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25">
-        <v>12806.8224518477</v>
-      </c>
-      <c r="F25">
-        <v>14700.4</v>
-      </c>
-      <c r="G25">
-        <v>14700.4</v>
+        <v>13020.4466708369</v>
+      </c>
+      <c r="F25" s="18">
+        <v>14700.3</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I25">
-        <v>40275.199999999997</v>
+        <v>44750.3</v>
       </c>
       <c r="J25">
-        <v>17260.8</v>
+        <v>19178.7</v>
       </c>
       <c r="K25">
-        <v>11749.2</v>
+        <v>13054.6</v>
       </c>
       <c r="L25">
-        <v>16068.2</v>
+        <v>17853.5</v>
       </c>
       <c r="M25">
-        <f t="shared" si="0"/>
-        <v>85353.4</v>
-      </c>
-      <c r="O25" s="4">
-        <v>17853.55</v>
-      </c>
-      <c r="P25" s="6">
-        <v>14673.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>94837.1</v>
+      </c>
+      <c r="O25" s="4"/>
+      <c r="P25" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>15874.78</v>
+      </c>
+      <c r="R25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="D26" s="5">
         <f>SUM(D22:D25)</f>
-        <v>93051.734948010999</v>
+        <v>100154.97000022281</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5">
         <f>SUM(F22:F25)</f>
-        <v>93051.7</v>
-      </c>
-      <c r="G26">
-        <f>SUM(G22:G25)</f>
-        <v>93051.9</v>
-      </c>
-      <c r="O26">
-        <f>SUM(O23:O25)*0.9</f>
-        <v>93051.755999999994</v>
-      </c>
-      <c r="P26">
-        <f>SUM(P23:P25)</f>
-        <v>93579.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+        <v>100154.90000000001</v>
+      </c>
+      <c r="Q26">
+        <f>SUM(Q23:Q25)</f>
+        <v>100154.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="7"/>
       <c r="B29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29">
-        <v>45180.308555776202</v>
+        <v>47513.203383841203</v>
       </c>
       <c r="F29">
-        <v>44469.599999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+        <v>47013.4</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>47236.4</v>
+      </c>
+      <c r="J29">
+        <v>20244.2</v>
+      </c>
+      <c r="K29">
+        <v>13779.9</v>
+      </c>
+      <c r="L29">
+        <v>16960.900000000001</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>98221.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30">
-        <v>19891.066801582099</v>
+        <v>25735.4466152645</v>
       </c>
       <c r="F30">
-        <v>20230.099999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+        <v>26235.3</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30">
+        <v>49722.5</v>
+      </c>
+      <c r="J30">
+        <v>21309.599999999999</v>
+      </c>
+      <c r="K30">
+        <v>13054.6</v>
+      </c>
+      <c r="L30">
+        <v>16068.2</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>100154.90000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31">
-        <v>13078.465217108</v>
+        <v>13594.8574070053</v>
       </c>
       <c r="F31">
-        <v>13651.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+        <v>13656.5</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31">
+        <v>44750.3</v>
+      </c>
+      <c r="J31">
+        <v>19178.7</v>
+      </c>
+      <c r="K31">
+        <v>14505.1</v>
+      </c>
+      <c r="L31">
+        <v>16068.2</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>94502.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
       <c r="B32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32">
-        <v>14901.9018941548</v>
+        <v>16547.3221760987</v>
       </c>
       <c r="F32">
-        <v>14700.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16485.7</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32">
+        <v>44750.3</v>
+      </c>
+      <c r="J32">
+        <v>19178.7</v>
+      </c>
+      <c r="K32">
+        <v>13054.6</v>
+      </c>
+      <c r="L32">
+        <v>17853.5</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>94837.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="8"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="5">
         <f>SUM(D29:D32)</f>
-        <v>93051.742468621102</v>
+        <v>103390.8295822097</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5">
-        <f t="shared" ref="F33" si="2">SUM(F29:F32)</f>
-        <v>93051.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="F33" si="3">SUM(F29:F32)</f>
+        <v>103390.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="7"/>
       <c r="D35">
-        <v>42079.177376984597</v>
+        <v>46309.624798052799</v>
       </c>
       <c r="F35">
-        <v>41667.599999999999</v>
-      </c>
-      <c r="H35" t="s">
+        <v>45138.7</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I35">
-        <v>38921.699999999997</v>
+        <v>43246.400000000001</v>
       </c>
       <c r="J35">
-        <v>16680.7</v>
+        <v>18534.2</v>
       </c>
       <c r="K35">
-        <v>11861.5</v>
+        <v>13179.5</v>
       </c>
       <c r="L35">
-        <v>12546.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13940.1</v>
+      </c>
+      <c r="M35">
+        <f t="shared" ref="M32:M36" si="4">SUM(I35:L35)</f>
+        <v>88900.200000000012</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="15"/>
+      <c r="S35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="7"/>
       <c r="D36">
-        <v>16449.7461214008</v>
+        <v>18722.525201230499</v>
       </c>
       <c r="F36">
-        <v>16861.3</v>
-      </c>
-      <c r="H36" t="s">
+        <v>19893.5</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I36">
-        <v>40970.300000000003</v>
+        <v>45522.5</v>
       </c>
       <c r="J36">
-        <v>17558.7</v>
+        <v>19509.599999999999</v>
       </c>
       <c r="K36">
-        <v>11237.3</v>
+        <v>12485.8</v>
       </c>
       <c r="L36">
-        <v>11885.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13206.4</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="4"/>
+        <v>90724.299999999988</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>65032.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="7"/>
       <c r="D37">
-        <v>12485.770545670101</v>
+        <v>13873.150417053001</v>
       </c>
       <c r="F37">
-        <v>12485.8</v>
-      </c>
-      <c r="H37" t="s">
+        <v>13873.2</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I37">
-        <v>36873.199999999997</v>
+        <v>40970.300000000003</v>
       </c>
       <c r="J37">
-        <v>15802.8</v>
+        <v>17558.7</v>
       </c>
       <c r="K37">
-        <v>12485.8</v>
+        <v>13873.1</v>
       </c>
       <c r="L37">
-        <v>11885.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13206.4</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="2"/>
+        <v>85608.5</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>13873.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="7"/>
       <c r="D38">
-        <v>13206.472288143401</v>
+        <v>14673.799825194799</v>
       </c>
       <c r="F38">
-        <v>13206.4</v>
-      </c>
-      <c r="H38" t="s">
+        <v>14673.8</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I38">
-        <v>36873.199999999997</v>
+        <v>40970.300000000003</v>
       </c>
       <c r="J38">
-        <v>15802.8</v>
+        <v>17558.7</v>
       </c>
       <c r="K38">
-        <v>11237.3</v>
+        <v>12485.8</v>
       </c>
       <c r="L38">
-        <v>13206.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14673.8</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="2"/>
+        <v>85688.6</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q38" s="11">
+        <v>14673.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="7"/>
       <c r="D39" s="5">
         <f>SUM(D35:D38)</f>
-        <v>84221.166332198904</v>
+        <v>93579.100241531094</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5">
         <f>SUM(F35:F38)</f>
-        <v>84221.099999999991</v>
+        <v>93579.199999999997</v>
+      </c>
+      <c r="Q39">
+        <f>SUM(Q36:Q38)</f>
+        <v>93579.1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="P16:Q16"/>
     <mergeCell ref="A21:A26"/>
     <mergeCell ref="A27:A32"/>
     <mergeCell ref="A34:A39"/>
@@ -2304,538 +2602,538 @@
   <sheetData>
     <row r="1" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
         <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>2012</v>
+        <v>2246.3000000000002</v>
       </c>
       <c r="F3">
-        <v>-1236.7</v>
+        <v>-1924</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>-1221.3</v>
+        <v>-336.6</v>
       </c>
       <c r="F4">
-        <v>1996.6</v>
+        <v>658.8</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>-363.9</v>
+        <v>-783.6</v>
       </c>
       <c r="F5">
-        <v>1139.5999999999999</v>
+        <v>1105.9000000000001</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" t="s">
         <v>45</v>
       </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
       <c r="P7" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>989.9</v>
+        <v>1110.5999999999999</v>
       </c>
       <c r="F12">
-        <v>-504.5</v>
+        <v>-1110.5999999999999</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>-1150.0999999999999</v>
+        <v>-257.3</v>
       </c>
       <c r="F13">
-        <v>1635.4</v>
+        <v>257.3</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>650</v>
+        <v>343.2</v>
       </c>
       <c r="F14">
-        <v>-164.7</v>
+        <v>-343.2</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" t="s">
-        <v>39</v>
-      </c>
       <c r="N16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="Q16" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="5" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
         <v>34</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>2136.6999999999998</v>
+        <v>2712.3</v>
       </c>
       <c r="F21">
-        <v>-1255.5999999999999</v>
+        <v>-1770.5</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E22">
-        <v>-399</v>
+        <v>402.6</v>
       </c>
       <c r="F22">
-        <v>1456.7</v>
+        <v>539.20000000000005</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E23">
-        <v>-476.7</v>
+        <v>-1389.2</v>
       </c>
       <c r="F23">
-        <v>1798.9</v>
+        <v>2331.9</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" t="s">
+        <v>85</v>
+      </c>
+      <c r="M25" t="s">
         <v>41</v>
       </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="N25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O25" t="s">
+        <v>45</v>
+      </c>
+      <c r="P25" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B28" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="F25" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" t="s">
-        <v>38</v>
-      </c>
-      <c r="J25" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" t="s">
-        <v>65</v>
-      </c>
-      <c r="L25" t="s">
-        <v>66</v>
-      </c>
-      <c r="M25" t="s">
-        <v>39</v>
-      </c>
-      <c r="N25" t="s">
-        <v>40</v>
-      </c>
-      <c r="O25" t="s">
-        <v>49</v>
-      </c>
-      <c r="P25" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
         <v>34</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E30">
-        <v>2528.9</v>
+        <v>3000</v>
       </c>
       <c r="F30">
-        <v>-1753.7</v>
+        <v>-2402.1999999999998</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E31">
-        <v>-1507.7</v>
+        <v>-751</v>
       </c>
       <c r="F31">
-        <v>2438</v>
+        <v>1548.1</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E32">
-        <v>-152.6</v>
+        <v>-947.6</v>
       </c>
       <c r="F32">
-        <v>1315.7</v>
+        <v>2143.3000000000002</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K34" t="s">
+        <v>76</v>
+      </c>
+      <c r="L34" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="N34" t="s">
+        <v>42</v>
+      </c>
+      <c r="O34" t="s">
+        <v>45</v>
+      </c>
+      <c r="P34" t="s">
         <v>78</v>
       </c>
-      <c r="G34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" t="s">
-        <v>37</v>
-      </c>
-      <c r="I34" t="s">
-        <v>38</v>
-      </c>
-      <c r="J34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K34" t="s">
-        <v>74</v>
-      </c>
-      <c r="L34" t="s">
-        <v>75</v>
-      </c>
-      <c r="M34" t="s">
-        <v>39</v>
-      </c>
-      <c r="N34" t="s">
-        <v>40</v>
-      </c>
-      <c r="O34" t="s">
-        <v>49</v>
-      </c>
-      <c r="P34" t="s">
-        <v>76</v>
-      </c>
       <c r="Q34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
